--- a/IPC_MZA empalmado.xlsx
+++ b/IPC_MZA empalmado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32C7C05E-9AEA-4A50-BA67-0CB596F44618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{32C7C05E-9AEA-4A50-BA67-0CB596F44618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4B23727-593E-48BF-992F-5AD50F93A166}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,12 +79,18 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -115,7 +121,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -134,7 +140,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1332,6 +1339,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="11.5546875" style="7"/>
+    <col min="7" max="7" width="11.5546875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1348,7 +1356,7 @@
         <v>5.7200000000000001E-2</v>
       </c>
       <c r="G1" s="8">
-        <f t="shared" ref="G1:G3" si="0">C1</f>
+        <f>C1</f>
         <v>147.28</v>
       </c>
     </row>
@@ -1374,7 +1382,7 @@
         <v>0.1011</v>
       </c>
       <c r="G2" s="8">
-        <f t="shared" si="0"/>
+        <f>C2</f>
         <v>167.48</v>
       </c>
     </row>
@@ -1389,18 +1397,18 @@
         <v>179.08</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D18" si="1">(B3-B2)/B2</f>
+        <f t="shared" ref="D3:D18" si="0">(B3-B2)/B2</f>
         <v>0.10600023438415582</v>
       </c>
       <c r="E3" s="7">
-        <f t="shared" ref="E3:E10" si="2">(C3-C2)/C2</f>
+        <f t="shared" ref="E3:E10" si="1">(C3-C2)/C2</f>
         <v>6.9262001433007064E-2</v>
       </c>
       <c r="F3" s="7">
         <v>9.3100000000000002E-2</v>
       </c>
       <c r="G3" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G1:G3" si="2">C3</f>
         <v>179.08</v>
       </c>
     </row>
@@ -1415,11 +1423,11 @@
         <v>194.89</v>
       </c>
       <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.16757615894039715</v>
+      </c>
+      <c r="E4" s="7">
         <f t="shared" si="1"/>
-        <v>0.16757615894039715</v>
-      </c>
-      <c r="E4" s="7">
-        <f t="shared" si="2"/>
         <v>8.828456555729268E-2</v>
       </c>
       <c r="F4" s="7">
@@ -1441,11 +1449,11 @@
         <v>211.61661758333335</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.23881477448044286</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" si="1"/>
-        <v>0.23881477448044286</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="2"/>
         <v>8.5825940701592524E-2</v>
       </c>
       <c r="F5" s="7">
@@ -1467,11 +1475,11 @@
         <v>224.88780650000001</v>
       </c>
       <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>0.14852935789897789</v>
+      </c>
+      <c r="E6" s="7">
         <f t="shared" si="1"/>
-        <v>0.14852935789897789</v>
-      </c>
-      <c r="E6" s="7">
-        <f t="shared" si="2"/>
         <v>6.2713359036846647E-2</v>
       </c>
       <c r="F6" s="7">
@@ -1493,11 +1501,11 @@
         <v>248.41401550000003</v>
       </c>
       <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25851511672407218</v>
+      </c>
+      <c r="E7" s="7">
         <f t="shared" si="1"/>
-        <v>0.25851511672407218</v>
-      </c>
-      <c r="E7" s="7">
-        <f t="shared" si="2"/>
         <v>0.1046130929290736</v>
       </c>
       <c r="F7" s="7">
@@ -1519,11 +1527,11 @@
         <v>272.69744600000001</v>
       </c>
       <c r="D8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.23850793168111095</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" si="1"/>
-        <v>0.23850793168111095</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" si="2"/>
         <v>9.7753866468134026E-2</v>
       </c>
       <c r="F8" s="7">
@@ -1545,11 +1553,11 @@
         <v>300.08478674999998</v>
       </c>
       <c r="D9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.23640381388877513</v>
+      </c>
+      <c r="E9" s="7">
         <f t="shared" si="1"/>
-        <v>0.23640381388877513</v>
-      </c>
-      <c r="E9" s="7">
-        <f t="shared" si="2"/>
         <v>0.10043123304499142</v>
       </c>
       <c r="F9" s="7">
@@ -1571,11 +1579,11 @@
         <v>331.95090075000002</v>
       </c>
       <c r="D10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.25908519229496269</v>
+      </c>
+      <c r="E10" s="7">
         <f t="shared" si="1"/>
-        <v>0.25908519229496269</v>
-      </c>
-      <c r="E10" s="7">
-        <f t="shared" si="2"/>
         <v>0.10619036821265995</v>
       </c>
       <c r="F10" s="7">
@@ -1594,7 +1602,7 @@
         <v>271.39999999999998</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.42684401451027792</v>
       </c>
       <c r="F11" s="7">
@@ -1613,7 +1621,7 @@
         <v>343.50750000000005</v>
       </c>
       <c r="D12" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.26568717759764215</v>
       </c>
       <c r="F12" s="7">
@@ -1632,7 +1640,7 @@
         <v>477.28499999999997</v>
       </c>
       <c r="D13" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.38944564529158721</v>
       </c>
       <c r="F13" s="7">
@@ -1651,7 +1659,7 @@
         <v>592.15750000000003</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.24067904920540154</v>
       </c>
       <c r="F14" s="7">
@@ -1670,7 +1678,7 @@
         <v>811.32299999999998</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.37011352554008004</v>
       </c>
       <c r="F15" s="7">
@@ -1689,7 +1697,7 @@
         <v>1257.57</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.55002384993399667</v>
       </c>
       <c r="F16" s="7">
@@ -1708,7 +1716,7 @@
         <v>1801.2225000000001</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.43230396717478964</v>
       </c>
       <c r="F17" s="7">
@@ -1727,7 +1735,7 @@
         <v>2703.9300000000003</v>
       </c>
       <c r="D18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.50116379292397262</v>
       </c>
       <c r="F18" s="7">
